--- a/grisha/exported_data.xlsx
+++ b/grisha/exported_data.xlsx
@@ -94,10 +94,18 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -465,6 +473,16 @@
   </sheetPr>
   <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13.2" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="9.6" customWidth="1" min="3" max="3"/>
+    <col width="13.2" customWidth="1" min="4" max="4"/>
+    <col width="8.4" customWidth="1" min="5" max="5"/>
+    <col width="14.4" customWidth="1" min="6" max="6"/>
+    <col width="20.4" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -549,6 +567,10 @@
   </sheetPr>
   <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16.8" customWidth="1" min="1" max="1"/>
+    <col width="20.4" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">

--- a/grisha/exported_data.xlsx
+++ b/grisha/exported_data.xlsx
@@ -9,12 +9,12 @@
   <sheets>
     <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="students" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Observability" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="VMware" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Artifacts" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="CI_CD" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Kubernetes" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Cloud Providers" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Cloud Providers" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Observability" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="VMware" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Artifacts" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="CI_CD" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Kubernetes" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Products" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
@@ -40,7 +40,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -61,8 +61,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
-        <bgColor rgb="00FFFF00"/>
+        <fgColor rgb="0000FF00"/>
+        <bgColor rgb="0000FF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF0000"/>
+        <bgColor rgb="00FF0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -92,12 +98,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -463,8 +480,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="20.4" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="9.6" customWidth="1" min="4" max="4"/>
+    <col width="13.2" customWidth="1" min="5" max="5"/>
+    <col width="8.4" customWidth="1" min="6" max="6"/>
+    <col width="14.4" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -474,32 +501,32 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Cloud Providers</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Observability</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>VMware</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Artifacts</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>CI/CD</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Kubernetes</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Cloud Providers</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -518,10 +545,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -533,6 +560,846 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Dmitrey Kazin</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Dor Mor</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Dan Sorozon</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Elad Tsciuba</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Elhanan Wexler</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Etai Hellman</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Gabi Titarenko</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Gal Frylich Bartal</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Grisha Sokolovsky</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Hay Katan</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Itai Rosenberg</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Kiril Kilakov</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Leonid Niraev</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Lior Burshan</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Dan Dolinsky</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Malki Feldman</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Michal Nevo Sarel</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Nadav Markus</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Netta Levy</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Boris Kodel</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ofer Hamberg</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Arthur Nikogosyan</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Vladimir Zheltov</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Avichai Kaykov</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Artium Shohat</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Tal Malchi</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Tal Naeh</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Ofer Ginsberg</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Valery Khirin</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Yona Bloy</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -549,6 +1416,10 @@
   </sheetPr>
   <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16.8" customWidth="1" min="1" max="1"/>
+    <col width="27.6" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -565,12 +1436,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Oz Pozner</t>
+          <t>Yona Bloy</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ozp@bynet.co.il</t>
+          <t>Yona.Bloy@bynet.co.il</t>
         </is>
       </c>
     </row>
@@ -585,12 +1456,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13.2" customWidth="1" min="1" max="1"/>
-    <col width="9.6" customWidth="1" min="2" max="2"/>
-    <col width="15.6" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="32.4" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -601,12 +1471,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>SPLUNK</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>AppDynamics</t>
+          <t>Azure Developer Assosiate</t>
         </is>
       </c>
     </row>
@@ -617,11 +1482,250 @@
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Dmitrey Kazin</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Dor Mor</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Dan Sorozon</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Elad Tsciuba</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Elhanan Wexler</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Etai Hellman</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Gabi Titarenko</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Gal Frylich Bartal</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Grisha Sokolovsky</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Hay Katan</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Itai Rosenberg</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Kiril Kilakov</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Leonid Niraev</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Lior Burshan</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Dan Dolinsky</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Malki Feldman</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Michal Nevo Sarel</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Nadav Markus</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Netta Levy</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Boris Kodel</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Ofer Hamberg</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Arthur Nikogosyan</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Vladimir Zheltov</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Avichai Kaykov</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Artium Shohat</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Tal Malchi</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Tal Naeh</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Ofer Ginsberg</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Valery Khirin</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Yona Bloy</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -634,10 +1738,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13.2" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="15.6" customWidth="1" min="2" max="2"/>
+    <col width="15.6" customWidth="1" min="3" max="3"/>
+    <col width="46.8" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -646,6 +1753,21 @@
           <t>Student</t>
         </is>
       </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Splunk</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>AppDynamics</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>ELK (Elasticsearch, Logstash, Kibana)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -653,6 +1775,317 @@
           <t>Oz Pozner</t>
         </is>
       </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>in_progress</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Dmitrey Kazin</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Dor Mor</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Dan Sorozon</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Elad Tsciuba</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Elhanan Wexler</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Etai Hellman</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Gabi Titarenko</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n"/>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Gal Frylich Bartal</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n"/>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Grisha Sokolovsky</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Hay Katan</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Itai Rosenberg</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Kiril Kilakov</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Leonid Niraev</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Lior Burshan</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Dan Dolinsky</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Malki Feldman</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Michal Nevo Sarel</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Nadav Markus</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Netta Levy</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Boris Kodel</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n"/>
+      <c r="C22" s="3" t="n"/>
+      <c r="D22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Ofer Hamberg</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Arthur Nikogosyan</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n"/>
+      <c r="C24" s="3" t="n"/>
+      <c r="D24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Vladimir Zheltov</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Avichai Kaykov</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="3" t="n"/>
+      <c r="D26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Artium Shohat</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Tal Malchi</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n"/>
+      <c r="C28" s="3" t="n"/>
+      <c r="D28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Tal Naeh</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Ofer Ginsberg</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n"/>
+      <c r="C30" s="3" t="n"/>
+      <c r="D30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Valery Khirin</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Yona Bloy</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n"/>
+      <c r="C32" s="3" t="n"/>
+      <c r="D32" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -665,10 +2098,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13.2" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="13.2" customWidth="1" min="2" max="2"/>
+    <col width="7.199999999999999" customWidth="1" min="3" max="3"/>
+    <col width="40.8" customWidth="1" min="4" max="4"/>
+    <col width="34.8" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -677,6 +2114,26 @@
           <t>Student</t>
         </is>
       </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>VSphere</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>NSX</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>TAP (Tanzu Application Platform)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TKG (Tanzu Kubernetes Grid)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -684,6 +2141,344 @@
           <t>Oz Pozner</t>
         </is>
       </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Dmitrey Kazin</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Dor Mor</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Dan Sorozon</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Elad Tsciuba</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Elhanan Wexler</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Etai Hellman</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Gabi Titarenko</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n"/>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Gal Frylich Bartal</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n"/>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Grisha Sokolovsky</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Hay Katan</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Itai Rosenberg</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Kiril Kilakov</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Leonid Niraev</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Lior Burshan</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Dan Dolinsky</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Malki Feldman</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Michal Nevo Sarel</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Nadav Markus</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Netta Levy</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Boris Kodel</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n"/>
+      <c r="C22" s="3" t="n"/>
+      <c r="D22" s="3" t="n"/>
+      <c r="E22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Ofer Hamberg</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Arthur Nikogosyan</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n"/>
+      <c r="C24" s="3" t="n"/>
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Vladimir Zheltov</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Avichai Kaykov</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="3" t="n"/>
+      <c r="D26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Artium Shohat</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Tal Malchi</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n"/>
+      <c r="C28" s="3" t="n"/>
+      <c r="D28" s="3" t="n"/>
+      <c r="E28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Tal Naeh</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Ofer Ginsberg</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n"/>
+      <c r="C30" s="3" t="n"/>
+      <c r="D30" s="3" t="n"/>
+      <c r="E30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Valery Khirin</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Yona Bloy</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n"/>
+      <c r="C32" s="3" t="n"/>
+      <c r="D32" s="3" t="n"/>
+      <c r="E32" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -696,10 +2491,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13.2" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8.4" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -708,6 +2504,11 @@
           <t>Student</t>
         </is>
       </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>JFrog</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -715,6 +2516,247 @@
           <t>Oz Pozner</t>
         </is>
       </c>
+      <c r="B2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Dmitrey Kazin</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Dor Mor</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Dan Sorozon</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Elad Tsciuba</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Elhanan Wexler</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Etai Hellman</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Gabi Titarenko</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Gal Frylich Bartal</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Grisha Sokolovsky</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Hay Katan</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Itai Rosenberg</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Kiril Kilakov</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Leonid Niraev</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Lior Burshan</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Dan Dolinsky</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Malki Feldman</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Michal Nevo Sarel</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Nadav Markus</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Netta Levy</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Boris Kodel</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Ofer Hamberg</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Arthur Nikogosyan</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Vladimir Zheltov</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Avichai Kaykov</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Artium Shohat</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Tal Malchi</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Tal Naeh</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Ofer Ginsberg</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Valery Khirin</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Yona Bloy</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -727,10 +2769,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13.2" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -744,6 +2786,216 @@
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Oz Pozner</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Dmitrey Kazin</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Dor Mor</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Dan Sorozon</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Elad Tsciuba</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Elhanan Wexler</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Etai Hellman</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Gabi Titarenko</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Gal Frylich Bartal</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Grisha Sokolovsky</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Hay Katan</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Itai Rosenberg</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Kiril Kilakov</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Leonid Niraev</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Lior Burshan</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Dan Dolinsky</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Malki Feldman</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Michal Nevo Sarel</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Nadav Markus</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Netta Levy</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Boris Kodel</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Ofer Hamberg</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Arthur Nikogosyan</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Vladimir Zheltov</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Avichai Kaykov</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Artium Shohat</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Tal Malchi</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Tal Naeh</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Ofer Ginsberg</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Valery Khirin</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Yona Bloy</t>
         </is>
       </c>
     </row>
@@ -758,10 +3010,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13.2" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="34.8" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -770,6 +3023,11 @@
           <t>Student</t>
         </is>
       </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>TKG (Tanzu Kubernetes Grid)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -777,6 +3035,247 @@
           <t>Oz Pozner</t>
         </is>
       </c>
+      <c r="B2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Dmitrey Kazin</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Dor Mor</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Dan Sorozon</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Elad Tsciuba</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Elhanan Wexler</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Etai Hellman</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Gabi Titarenko</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Gal Frylich Bartal</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Grisha Sokolovsky</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Hay Katan</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Itai Rosenberg</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Kiril Kilakov</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Leonid Niraev</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Lior Burshan</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Dan Dolinsky</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Malki Feldman</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Michal Nevo Sarel</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Nadav Markus</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Netta Levy</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Boris Kodel</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Ofer Hamberg</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Arthur Nikogosyan</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Vladimir Zheltov</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Avichai Kaykov</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Artium Shohat</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Tal Malchi</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Tal Naeh</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Ofer Ginsberg</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Valery Khirin</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Yona Bloy</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -789,10 +3288,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13.2" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,6 +3308,216 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Dmitrey Kazin</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Dor Mor</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Dan Sorozon</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Elad Tsciuba</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Elhanan Wexler</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Etai Hellman</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Gabi Titarenko</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Gal Frylich Bartal</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Grisha Sokolovsky</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Hay Katan</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Itai Rosenberg</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Kiril Kilakov</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Leonid Niraev</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Lior Burshan</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Dan Dolinsky</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Malki Feldman</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Michal Nevo Sarel</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Nadav Markus</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Netta Levy</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Boris Kodel</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Ofer Hamberg</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Arthur Nikogosyan</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Vladimir Zheltov</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Avichai Kaykov</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Artium Shohat</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Tal Malchi</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Tal Naeh</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Ofer Ginsberg</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Valery Khirin</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Yona Bloy</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
